--- a/BilanSujets.xlsx
+++ b/BilanSujets.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\TP_Sujets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A90B92E-C90A-4DE3-9A83-B4370AB48818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1041D834-B55F-4420-B89A-3F6905E39943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sujets" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="Bilan_2026" sheetId="3" r:id="rId1"/>
+    <sheet name="Sujets" sheetId="1" r:id="rId2"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
   <si>
     <t>Chaine fonctionnelle du système</t>
   </si>
@@ -395,6 +396,24 @@
   </si>
   <si>
     <t>Attelle CPM 130</t>
+  </si>
+  <si>
+    <t>Mise en service</t>
+  </si>
+  <si>
+    <t>Mise en service rapide</t>
+  </si>
+  <si>
+    <t>Existe + Vérif ok</t>
+  </si>
+  <si>
+    <t>Existe + à vérifier</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>MaxPIDE</t>
   </si>
 </sst>
 </file>
@@ -457,7 +476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,6 +525,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="37">
     <border>
@@ -993,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1220,6 +1257,99 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1500,6 +1630,697 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E975A67-6676-44A8-92CE-1726D77AF678}">
+  <dimension ref="A1:Q32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="5.453125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="5.453125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="112">
+        <v>1</v>
+      </c>
+      <c r="D1" s="112"/>
+      <c r="E1" s="4">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4">
+        <v>6</v>
+      </c>
+      <c r="L1" s="4">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4">
+        <v>9</v>
+      </c>
+      <c r="O1" s="4">
+        <v>10</v>
+      </c>
+      <c r="P1" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="80"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="77"/>
+      <c r="I2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="80"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="N3" s="65" t="s">
+        <v>107</v>
+      </c>
+      <c r="O3" s="20"/>
+      <c r="P3" s="24"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
+        <v>2</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="12">
+        <v>3</v>
+      </c>
+      <c r="B6" s="111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="12">
+        <v>4</v>
+      </c>
+      <c r="B7" s="110" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="12">
+        <v>5</v>
+      </c>
+      <c r="B8" s="110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="12">
+        <v>6</v>
+      </c>
+      <c r="B9" s="110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="91"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="12">
+        <v>7</v>
+      </c>
+      <c r="B10" s="110" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="12">
+        <v>8</v>
+      </c>
+      <c r="B11" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="96"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
+        <v>10</v>
+      </c>
+      <c r="B13" s="110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="89"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="89"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="12">
+        <v>11</v>
+      </c>
+      <c r="B14" s="110" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="12">
+        <v>11</v>
+      </c>
+      <c r="B15" s="110" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="12">
+        <v>12</v>
+      </c>
+      <c r="B16" s="110" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="12">
+        <v>13</v>
+      </c>
+      <c r="B17" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="12">
+        <v>14</v>
+      </c>
+      <c r="B18" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="12">
+        <v>15</v>
+      </c>
+      <c r="B19" s="110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
+        <v>16</v>
+      </c>
+      <c r="B20" s="110" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="93"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="12">
+        <v>17</v>
+      </c>
+      <c r="B21" s="110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="93"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="12">
+        <v>18</v>
+      </c>
+      <c r="B22" s="110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A23" s="12">
+        <v>19</v>
+      </c>
+      <c r="B23" s="110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A24" s="12">
+        <v>20</v>
+      </c>
+      <c r="B24" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>21</v>
+      </c>
+      <c r="B25" s="110" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="94"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="13">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="105"/>
+      <c r="P26" s="105"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13">
+        <v>25</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="102"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="105"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C29" s="106"/>
+      <c r="D29" s="107" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C30" s="108"/>
+      <c r="D30" s="107" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C31" s="109"/>
+      <c r="D31" s="107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2382,7 +3203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
